--- a/gen_ai_apps_horizontal_vs_vertical.xlsx
+++ b/gen_ai_apps_horizontal_vs_vertical.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="Horizontal AI Apps" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Vertical AI Apps" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Horizontal vs Vertical Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Market Share Trends" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ARPU Comparison" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Horizontal vs Vertical Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Market Share Trends" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -511,14 +512,16 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="55" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Horizontal (General-Purpose) Generative AI Apps — Usage &amp; Downloads</t>
+          <t>Horizontal (General-Purpose) Generative AI Apps — Usage, Downloads &amp; ARPU</t>
         </is>
       </c>
     </row>
@@ -540,7 +543,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Monthly Active Users
+          <t>MAU
 (Mobile, Feb 2026)</t>
         </is>
       </c>
@@ -575,6 +578,17 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
+          <t>Revenue / ARR</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Est. ARPU
+(Blended, $/mo)</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -585,7 +599,7 @@
           <t>ChatGPT</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
@@ -622,12 +636,22 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>900M WAU</t>
+          <t>900M</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>Largest consumer AI product; declining share but dominant scale</t>
+          <t>$25B ARR (annualized, early 2026)</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>~$4-6 (blended free+paid); $20/mo Plus, $200/mo Pro</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Largest consumer AI product; 22M paid subs (~7% conversion); testing ads</t>
         </is>
       </c>
     </row>
@@ -637,7 +661,7 @@
           <t>Google Gemini</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
@@ -649,7 +673,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>114.9M</t>
+          <t>750M (incl. Search AI)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -679,7 +703,17 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Strong web traffic; pre-installed on Android; Nano Banana drove 10M new users</t>
+          <t>$1.2B subs revenue (2025); 8M+ enterprise seats</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>~$1-2 (blended); $20/mo Advanced; $30/mo Enterprise</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>Pre-installed on Android; Nano Banana drove 10M new users; 325M total Google subs</t>
         </is>
       </c>
     </row>
@@ -689,7 +723,7 @@
           <t>Claude</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Anthropic</t>
         </is>
@@ -701,7 +735,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>18.9M</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -731,7 +765,17 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Fastest DAU growth; 167% MoM jump in Mar 2026; 139 min/day power user time</t>
+          <t>$19B ARR (Mar 2026); incl. $2.5B Claude Code</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>~$20 (Pro); ~$100 (Team); enterprise &gt;&gt;$100</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>Fastest DAU growth; 167% MoM jump Mar 2026; 80% rev from enterprise; 500+ customers &gt;$1M/yr</t>
         </is>
       </c>
     </row>
@@ -741,7 +785,7 @@
           <t>Grok</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>xAI</t>
         </is>
@@ -753,7 +797,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>64M (Sep 2025)</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -783,7 +827,17 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Integrated into X/Twitter; declining share from 15.3%</t>
+          <t>~$500M ARR (xAI standalone, 2025); X subs $1B ARR</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Bundled with X Premium ($8-16/mo)</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>Integrated into X/Twitter; SpaceX acquired xAI Feb 2026; $230B valuation</t>
         </is>
       </c>
     </row>
@@ -793,7 +847,7 @@
           <t>Microsoft Copilot</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
@@ -835,7 +889,17 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Bundled with Windows/Office; enterprise-focused</t>
+          <t>~$1.5-2.5B (M365 Copilot, after discounts); 15M paid seats</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>$30/user/mo (list); ~$12-18 effective (40-60% discounts)</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>3.3% conversion of 450M M365 base; 160% seat growth YoY; 90% of Fortune 100</t>
         </is>
       </c>
     </row>
@@ -845,7 +909,7 @@
           <t>DeepSeek</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>DeepSeek (China)</t>
         </is>
@@ -887,7 +951,17 @@
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Bridges China/Russia/US markets; strong open-source model</t>
+          <t>$1.1B total rev (2025); 55% from API</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Primarily API-based pricing (low consumer ARPU)</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>Bridges China/Russia/US; 28-32% net margin; open-source models</t>
         </is>
       </c>
     </row>
@@ -897,7 +971,7 @@
           <t>Perplexity</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Perplexity AI</t>
         </is>
@@ -909,7 +983,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>15M+</t>
+          <t>30M+</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -939,7 +1013,17 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>AI-first search; Comet browser launched; 100M queries/week</t>
+          <t>$450M ARR (Mar 2026); up 50% in one month</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>$20/mo Pro; $200/mo Max; ~60-65% rev from subs</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>AI-first search; Comet browser; 780M queries/mo; $20B valuation</t>
         </is>
       </c>
     </row>
@@ -949,7 +1033,7 @@
           <t>Doubao (豆包)</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>ByteDance</t>
         </is>
@@ -990,6 +1074,16 @@
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>N/A (ByteDance private)</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Freemium (China pricing)</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>China market; 87% MoM MAU growth; ByteDance ecosystem</t>
         </is>
@@ -1001,7 +1095,7 @@
           <t>Qwen (千问)</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Alibaba</t>
         </is>
@@ -1042,6 +1136,16 @@
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>N/A (Alibaba Cloud bundled)</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Freemium + API (China pricing)</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>China market; 553% MoM growth; open-source models</t>
         </is>
@@ -1053,7 +1157,7 @@
           <t>Quark (夸克)</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Alibaba</t>
         </is>
@@ -1095,13 +1199,23 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>China market; AI-powered search + productivity</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Freemium (China pricing)</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>China market; AI-powered search + productivity suite</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1113,24 +1227,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="55" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Vertical (Specialized) Generative AI Apps — Usage &amp; Downloads</t>
+          <t>Vertical (Specialized) Generative AI Apps — Usage, Downloads, Revenue &amp; ARPU</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1268,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Monthly Active Users
+          <t>MAU
 (Mobile/Web)</t>
         </is>
       </c>
@@ -1169,15 +1285,26 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
+          <t>Est. ARPU
+($/mo)</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>Pricing Tiers</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
           <t>Key AI Features</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1197,6 +1324,8 @@
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1204,7 +1333,7 @@
           <t>Midjourney</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Midjourney</t>
         </is>
@@ -1216,7 +1345,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>~12M active</t>
+          <t>~12M active users</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1226,22 +1355,32 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>~$400M (2024)</t>
+          <t>$500M rev (2025)</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Text-to-image generation, style controls</t>
+          <t>~$10 (est. $120/yr ARPU)</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Declining rank (#46 on a16z list, down from top 10)</t>
+          <t>$10/mo Basic, $30 Standard, $60 Pro</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Squeezed by ChatGPT &amp; Gemini native image gen</t>
+          <t>Text-to-image, style controls, inpainting</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Declining rank (#46, was top 10)</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>40 employees; no VC; squeezed by ChatGPT/Gemini native image gen</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1390,7 @@
           <t>Leonardo.AI</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Leonardo Interactive</t>
         </is>
@@ -1278,15 +1417,25 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
+          <t>~$10-24/mo (paid tiers)</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>$10/mo, $24/mo, $48/mo</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
           <t>Image gen, model training, creative workflows</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Stable</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Serves creative communities with opinionated features</t>
         </is>
@@ -1298,7 +1447,7 @@
           <t>Ideogram</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Ideogram</t>
         </is>
@@ -1325,15 +1474,25 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>$8/mo Basic, $20/mo Plus</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
           <t>Text-in-image gen, typography-aware models</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>Growing</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Differentiated on text rendering quality</t>
         </is>
@@ -1353,16 +1512,18 @@
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>PixVerse</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>PixVerse</t>
+          <t>Runway</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Runway ML</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1372,44 +1533,54 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>24.8M MAU</t>
+          <t>1.2M MAU; 500K WAC</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A (web-based)</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$112.6M rev (2025); targeting $265M ARR (2026)</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>AI video generation, effects</t>
+          <t>~$12 Standard; $28 Pro; $76 Unlimited</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Growing</t>
+          <t>$12/mo, $28/mo, $76/mo</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Leading video gen app by MAU</t>
+          <t>Gen-4.5 text-to-video, image-to-video, camera controls</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Growing (150K paying users)</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>$5.3B valuation; $860M total funding; 4M registered users</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Kling AI</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Kuaishou</t>
+          <t>PixVerse</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>PixVerse</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1419,7 +1590,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>9.8M MAU</t>
+          <t>24.8M MAU</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1434,96 +1605,158 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>AI image &amp; video generation</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
+          <t>Freemium + credits</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>AI video generation, effects</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
           <t>Growing</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>Chinese-developed; leading quality</t>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Leading video gen app by MAU</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>Kling AI</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Kuaishou</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Video Generation</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>9.8M MAU</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Freemium + credits</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>AI image &amp; video generation</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>Growing</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Chinese-developed; leading output quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>Sora</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>OpenAI</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Video Generation</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>~3M DAU (mobile)</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>1M+ (first month)</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>N/A (bundled with ChatGPT Plus/Pro)</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Bundled ($20-200/mo ChatGPT plans)</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Included in ChatGPT Plus/Pro</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Text-to-video, Cameo (real people)</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>Cooling after launch spike</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>20 days at #1 US App Store; downloads declining</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Creative — Music &amp; Voice</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>20 days at #1 US App Store; downloads declining post-launch</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Suno</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Suno</t>
+          <t>Synthesia</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Synthesia</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Music Generation</t>
+          <t>AI Video (Enterprise)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1538,81 +1771,61 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$100M+ ARR (Apr 2025)</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>AI music/song generation</t>
+          <t>~$22 Starter; enterprise &gt;&gt;$100/seat</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Stable (#15 on a16z web list)</t>
+          <t>$22/mo Starter, custom Enterprise</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>Defensible niche; not replicated by big platforms</t>
+          <t>AI avatar video gen, multilingual dubbing</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Growing</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>70% of Fortune 100 as customers; Adobe Ventures investor</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>ElevenLabs</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>ElevenLabs</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Voice / Audio</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>Voice cloning, dubbing, audio production</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Stable (on every a16z edition)</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>Specialized enough to resist commoditization</t>
-        </is>
-      </c>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Creative — Music &amp; Voice</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Rythmix</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Rythmix</t>
+          <t>Suno</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Suno</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1622,7 +1835,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>1.4M MAU</t>
+          <t>100M+ total users; 2M paid subs</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1632,64 +1845,116 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$300M ARR (Feb 2026)</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>AI music generation</t>
+          <t>~$12.50 (est. from $300M/2M subs)</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Growing</t>
+          <t>$10/mo Pro, $30/mo Premier</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Smaller player in music gen space</t>
+          <t>AI music/song generation from text</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Explosive growth (+50% in 3 months)</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>$2.45B valuation; 203 employees; defensible niche</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Creative — Design &amp; Editing (AI-Enhanced)</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>ElevenLabs</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>ElevenLabs</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Voice / Audio</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>$330M ARR (Apr 2026)</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>~$5 Starter; $22 Creator; $99 Pro</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>$5/mo, $22/mo, $99/mo, $199/mo</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Voice cloning, dubbing, audio production, TTS</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Growing ($11B valuation)</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Launched ElevenMusic (Apr 2026); on every a16z edition; specialized moat</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>CapCut</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>ByteDance</t>
+          <t>Rythmix</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Rythmix</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Video Editing</t>
+          <t>Music Generation</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>736M MAU (mobile)</t>
+          <t>1.4M MAU</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>509.2M (2025)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1699,148 +1964,180 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>BG removal, AI effects, auto-captions, text-to-video</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Dominant</t>
+          <t>Freemium</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Largest AI-enhanced creative app by MAU</t>
+          <t>AI music generation</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Growing</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Smaller player in music gen space</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Canva</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Canva</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Design</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>265M MAU</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>$2.5B+ ARR (est.)</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>Magic Suite: AI image gen, text-to-design, app builder</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>Growing</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>31M paying subs; AI app builder has 10M MAU</t>
-        </is>
-      </c>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Creative — Design &amp; Editing (AI-Enhanced)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Picsart</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Picsart</t>
+          <t>CapCut</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Photo/Video Editing</t>
+          <t>Video Editing</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>150M MAU</t>
+          <t>736M MAU (mobile)</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>509.2M (2025)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$815M rev (2025)</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>AI Image Gen, outpainting, BG remover, AI agents</t>
+          <t>~$0.09 (blended); $2.49-$7.49/mo subs</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>$2.49/mo (100GB), $7.49/mo (1TB); in-app purchases</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>AI-powered creative suite</t>
+          <t>BG removal, AI effects, auto-captions, text-to-video</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Dominant</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>81% of mobile video editing market; Seedance 2.0 integration coming</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Coding &amp; Developer Tools</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-      <c r="I20" s="7" t="n"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Canva</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Canva</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>265M MAU</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>$4B rev (2025)</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>~$1.27 (blended); $15/mo Pro; ~$10/seat Teams</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Free, $15/mo Pro, $10/seat Teams, Enterprise custom</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Magic Suite: AI image gen, text-to-design, app builder</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Growing</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>31M paying subs; AI app builder has 10M MAU; $40B+ valuation</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Cursor</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Anysphere</t>
+          <t>Picsart</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Picsart</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Code Editor</t>
+          <t>Photo/Video Editing</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>150M MAU</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1855,34 +2152,44 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>AI code completion, chat, agent mode</t>
+          <t>~$5 Gold; $7 Platinum/mo</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Growing (on a16z top 50 web)</t>
+          <t>$5/mo Gold, $7/mo Platinum</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>AI-native code editor; developer-focused</t>
+          <t>AI Image Gen, outpainting, BG remover, AI agents</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>AI-powered creative suite; broad consumer base</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Claude Code</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
+          <t>Descript</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Descript</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>CLI Coding Agent</t>
+          <t>Video/Audio Editing</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1897,210 +2204,294 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>$1B ARR (run rate)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Command-line coding agent</t>
+          <t>$24 Hobbyist; $33 Pro/mo</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>Explosive growth</t>
+          <t>$24/mo Hobbyist, $33/mo Pro</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>$1B ARR in 6 months; 2M+ WAU</t>
+          <t>AI transcription, text-based video editing, screen recording</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Podcast/video creators; text-based editing paradigm</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Lovable</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Lovable</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>App Builder</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>~8M users</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>$200M ARR</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>AI app/website builder from prompts</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Growing</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>100K+ projects/day; $6.6B valuation</t>
-        </is>
-      </c>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Coding &amp; Developer Tools</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="7" t="n"/>
+      <c r="I23" s="7" t="n"/>
+      <c r="J23" s="7" t="n"/>
+      <c r="K23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Replit</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Replit</t>
+          <t>GitHub Copilot</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft / GitHub</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Code / App Builder</t>
+          <t>Code Assistant</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>20M+ total users</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A (IDE plugin)</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~$500M-1B (est.); 4.7M paid subs</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>AI coding, deployment, collaboration</t>
+          <t>$10/mo Individual; $19 Business; $39 Enterprise</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Stable (on a16z list)</t>
+          <t>$10/mo, $19/mo, $39/mo</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Browser-based coding with AI agent</t>
+          <t>Code completion, chat, agent mode, multi-model</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Growing (75% YoY paid growth)</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>90% of Fortune 100; most widely adopted AI coding tool</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>AI Companions</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="n"/>
-      <c r="G25" s="7" t="n"/>
-      <c r="H25" s="7" t="n"/>
-      <c r="I25" s="7" t="n"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Anysphere</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Code Editor</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>1M+ MAU (late 2025)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>N/A (desktop app)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>$2B ARR (Feb-Mar 2026)</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>$20/mo Pro; $40/mo Business</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>$20/mo Pro, $40/mo Business</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>AI code completion, chat, agent, multi-file edits</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Explosive growth (doubled ARR in 3 months)</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>$60B valuation (discussions Apr 2026); 60% enterprise revenue</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Character.AI</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Character Technologies</t>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>AI Companion / Chat</t>
+          <t>CLI Coding Agent</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>20M MAU</t>
+          <t>2M+ WAU (Mar 2026)</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>~69M total</t>
+          <t>N/A (CLI tool)</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>$32.2M rev (2024)</t>
+          <t>$2.5B ARR run rate (Feb 2026)</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>User-created chatbots, roleplay, conversation</t>
+          <t>Usage-based via Claude Max ($100-200/mo)</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Declining from 28M peak</t>
+          <t>Included in Claude Pro/Max; usage-based</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Core demo: 75% aged 18-34; 2 hrs/day usage</t>
+          <t>Command-line agentic coding, multi-step tasks</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Explosive growth</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>$1B ARR in 6 months; fastest-growing Anthropic product</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Writing &amp; Productivity (AI-Enhanced)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
-      <c r="I27" s="7" t="n"/>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>App Builder</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>~8M users</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>N/A (web-based)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>$400M ARR (Feb 2026)</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>$25 Pro; $50 Business/mo</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>$25/mo Pro, $50/mo Business, Enterprise custom</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>AI app/website builder from prompts</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Explosive growth</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>100K+ projects/day; $6.6B valuation; 146 employees</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Grammarly</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Grammarly</t>
+          <t>Replit</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Replit</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Writing Assistant</t>
+          <t>Code / App Builder</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2115,123 +2506,153 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$265M ARR (2025)</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>AI writing suggestions, tone, rewriting</t>
+          <t>$25/mo Replit Core</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>$0 (free), $25/mo Core</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Top AI writing assistant; embedded in workflows</t>
+          <t>AI coding, deployment, collaboration, agent</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Explosive (1,556% YoY growth)</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>150K+ paying customers; $9B valuation; browser-based</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Notion</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Notion Labs</t>
+          <t>Windsurf (Codeium)</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Codeium</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Productivity / Docs</t>
+          <t>Code Editor</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>800K+ developers</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A (desktop app)</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>~50% ARR from AI</t>
+          <t>$82M ARR (Jul 2025)</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>AI writing, research agents, notetakers, automation</t>
+          <t>$15/mo Pro; $40/mo Team</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
+          <t>$15/mo Pro, $40/mo Team</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>AI code completion, chat, multi-file agent</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
           <t>Growing</t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>AI attach rate surged 20% → 50% in one year</t>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>$1.25B valuation; 100B+ tokens/day; proposed $3B OpenAI acquisition failed</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>QuillBot</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Course Hero</t>
+          <t>OpenAI Codex</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Writing / Paraphrase</t>
+          <t>Coding Agent</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2M WAU (Mar 2026)</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A (Mac app)</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Bundled with ChatGPT Pro ($200/mo)</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>AI paraphrasing, grammar, summarization</t>
+          <t>Bundled ($200/mo ChatGPT Pro)</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Stable</t>
+          <t>Included in ChatGPT Pro/Team/Enterprise</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Popular with students and writers</t>
+          <t>Standalone coding agent, multi-step tasks</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Growing (25% weekly WAU growth)</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>3M users + 9M business users; 40% of OpenAI rev from enterprise</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>Search &amp; Research</t>
+          <t>Legal &amp; Professional Services</t>
         </is>
       </c>
       <c r="B31" s="7" t="n"/>
@@ -2242,269 +2663,906 @@
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="7" t="n"/>
       <c r="I31" s="7" t="n"/>
+      <c r="J31" s="7" t="n"/>
+      <c r="K31" s="7" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Gauth</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>ByteDance</t>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Harvey AI</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Education / Study</t>
+          <t>Legal AI</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>7.0M MAU</t>
+          <t>74K+ lawyers</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A (enterprise SaaS)</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>$190M ARR (2025); up 280% from $50M (2024)</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>AI homework help, math solving</t>
+          <t>~$214/user/mo (est. $190M/74K users)</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Growing</t>
+          <t>Enterprise contracts (custom pricing)</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>AI study companion</t>
+          <t>Contract analysis, legal research, due diligence, drafting</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>Explosive growth</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>$1.5B valuation; 1,000+ customers across 60+ countries; 95% contract accuracy</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Question.AI</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>ByteDance</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Education / Study</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>5.7M MAU</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>AI math solving, homework help</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="inlineStr">
-        <is>
-          <t>Growing</t>
-        </is>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>Math-focused AI tool</t>
-        </is>
-      </c>
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>AI Companions</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="7" t="n"/>
+      <c r="I33" s="7" t="n"/>
+      <c r="J33" s="7" t="n"/>
+      <c r="K33" s="7" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Agents &amp; Automation</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Character.AI</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Character Technologies</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>AI Companion / Chat</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>20M MAU</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>~69M total</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>$32-50M rev (2025)</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>~$0.13 (blended); $9.99/mo c.ai+</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Free, $9.99/mo c.ai+</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>User-created chatbots, roleplay, conversation</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Declining from 28M peak</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>75% aged 18-34; 2 hrs/day usage; ARPU ceiling challenge</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>OpenClaw</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>OpenAI (acquired)</t>
+          <t>Replika</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Luka</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Horizontal Agent</t>
+          <t>AI Companion / Chat</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>68K GitHub stars</t>
+          <t>30M DAU (claimed)</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>10M+ total</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>~$35M rev (2026 est.)</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Multi-step task execution across apps</t>
+          <t>~$19.99/mo (paid tier)</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Explosive growth</t>
+          <t>Free, $19.99/mo Pro</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Most-starred GitHub project; acquired by OpenAI Feb 2026</t>
+          <t>AI companion, emotional support, roleplay</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Flat/declining</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>~25% free-to-paid conversion; cost scales with engagement (superfan paradox)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Manus</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Meta (acquired)</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Task Agent</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>Open-ended task execution (research, slides, sheets)</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>Growing</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>Acquired by Meta for ~$2B; on a16z list twice</t>
-        </is>
-      </c>
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Writing &amp; Productivity (AI-Enhanced)</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
+      <c r="J36" s="7" t="n"/>
+      <c r="K36" s="7" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
+          <t>Grammarly</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Grammarly</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Writing Assistant</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>40M DAU</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>10M+ (Chrome ext.)</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>$700M+ rev (2026); profitable</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>~$1.46 (blended); $12 Premium; $15/seat Business</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Free, $12/mo Premium, $15/seat Business</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>AI writing suggestions, tone, rewriting, gen AI features</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Stable/Growing</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>96% of Fortune 500; 70K enterprise customers; $13B valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Notion Labs</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Productivity / Docs</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>100M+ total users; 20M MAU</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>$500-540M ARR (Sep 2025); ~50% from AI</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>~$10 Plus; $18/seat Business; AI add-on $10/seat</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>$10/mo Plus, $18/seat Business, AI $10/seat add-on</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>AI writing, research agents, notetakers, task automation</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Growing</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>AI attach rate 20% → 50% in one year; $11B valuation; 75% of Fortune 500</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Jasper</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Jasper AI</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Marketing Copy / Writing</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>1.8M MAU</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>$88M rev (2025); down from $120M peak (2023)</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>~$69/mo (est.)</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>$39/mo Creator, $59/mo Pro, custom Business</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>AI marketing copy, brand voice, campaigns</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Declining (revenue fell from peak)</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>800K orgs; $1.5B valuation; pivoting to enterprise; high ARPU but shrinking base</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>QuillBot</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Course Hero</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Writing / Paraphrase</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>~$8.33/mo (annual plan)</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>$9.95/mo, $6.66/mo (annual)</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>AI paraphrasing, grammar, summarization</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Stable</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>Popular with students and writers</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>AI Notetakers / Meeting AI</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="7" t="n"/>
+      <c r="I41" s="7" t="n"/>
+      <c r="J41" s="7" t="n"/>
+      <c r="K41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Otter.ai</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Otter.ai</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Meeting Transcription</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>35M users</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>$100M+ ARR (Mar 2025)</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>~$8.33 Pro; $20 Business; $25 Enterprise/mo</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>$8.33/mo Pro, $20/mo Business, $25/mo Enterprise</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>AI transcription, meeting summaries, action items, knowledge base</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Growing</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>&lt;200 employees; $500K rev/employee; evolved from transcription to knowledge platform</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Fireflies.ai</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Fireflies</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Meeting Transcription</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>175K+ users</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>$10 Pro; $19 Business; $39 Enterprise/mo</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>$10/mo Pro, $19/mo Business, $39/mo Enterprise</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>AI transcription, conversation intelligence, CRM integration</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Growing</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>10K+ companies; 40% of Fortune 500; 500K min/day transcribed</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Education / Study AI</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="7" t="n"/>
+      <c r="I44" s="7" t="n"/>
+      <c r="J44" s="7" t="n"/>
+      <c r="K44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Gauth</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Education / Study</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>7.0M MAU</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Freemium</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>AI homework help, math solving, step-by-step</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>Growing</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>AI study companion; ByteDance ecosystem</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Question.AI</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Education / Study</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>5.7M MAU</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Freemium</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>AI math solving, homework help</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>Growing</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>Math-focused AI tool</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Agents &amp; Automation</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
+      <c r="J47" s="7" t="n"/>
+      <c r="K47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>OpenClaw</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>OpenAI (acquired)</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Horizontal Agent</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>68K GitHub stars</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>N/A (open-source)</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>N/A (self-hosted)</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Free / open-source</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>Multi-step task execution across messaging apps</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>Explosive growth</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>Most-starred GitHub project; acquired by OpenAI Feb 2026; requires Terminal</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Manus</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Meta (acquired)</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Task Agent</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>Open-ended task execution (research, slides, sheets)</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>Growing</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>Acquired by Meta for ~$2B Dec 2025; on a16z list twice</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
           <t>Genspark</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Genspark</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Task Agent</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>$100M ARR</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>End-to-end task workflows, research</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>End-to-end task workflows, research agents</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>Growing</t>
         </is>
       </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>$300M Series B; debuted on a16z list</t>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>$300M Series B; debuted on a16z 6th edition list</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A27:I27"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A16:I16"/>
+  <mergeCells count="12">
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A47:K47"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A44:K44"/>
+    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="A8:K8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2516,273 +3574,1423 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="55" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Horizontal vs Vertical Gen AI Apps — Comparative Summary</t>
+          <t>Gen AI App ARPU Comparison — Horizontal vs Vertical</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>App</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Horizontal Apps</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Vertical Apps</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Key Insight</t>
+          <t>Blended ARPU
+($/mo, est.)</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Paid Tier ARPU
+($/mo)</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Revenue / ARR</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Paid Users / Subs</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>ARPU Notes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Market Concentration</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Extremely high — top 2 (ChatGPT + Gemini) hold ~64% of DAU share in US</t>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Fragmented across many categories; CapCut (736M MAU) is the single largest but in video editing only</t>
+          <t>Legal AI</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Horizontal apps consolidate users; vertical apps compete within niches</t>
+          <t>~$214</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>$214+ (enterprise)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>$190M ARR</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>74K lawyers</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Highest ARPU; enterprise-only pricing; custom contracts</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Total Downloads (2025)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>~1.35B+ (ChatGPT 845M + Gemini 305M + DeepSeek 110M + Grok 88M)</t>
+          <t>Jasper</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>CapCut alone: 509M; total across top 500 AI apps: 2.7B (horizontal + vertical)</t>
+          <t>Marketing Copy</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Horizontal chatbots dominate downloads but AI-enhanced tools (CapCut, Canva) have massive reach</t>
+          <t>~$69</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>$39-59+</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>$88M rev (2025)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>100K customers</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>High ARPU but declining user base; enterprise pivot</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MAU Scale</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>ChatGPT: 955M; Doubao: 315M; Qwen: 203M; DeepSeek: 133M; Gemini: 115M</t>
+          <t>Microsoft Copilot (M365)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>CapCut: 736M; Canva: 265M; Picsart: 150M; Character.AI: 20M; Perplexity: 15M</t>
+          <t>AI Assistant (Enterprise)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>AI-enhanced creative tools rival horizontal assistants in scale</t>
+          <t>~$12-18 (effective)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>$30 (list price)</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>~$1.5-2.5B (est.)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>15M seats</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Heavy discounting (40-60%); $30 list price rarely paid in full</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Revenue Model</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Subscriptions ($20/mo typical); ChatGPT testing ads; transaction take-rate planned</t>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Freemium + subscriptions; credits/usage-based; some enterprise licensing</t>
+          <t>Code Editor</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Horizontal apps moving toward super-app monetization; vertical apps monetize niche depth</t>
+          <t>~$20-40</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>$20 Pro; $40 Business</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>$2B ARR</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>1M+ MAU</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>60% enterprise; doubling ARR every 3 months</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Growth Trajectory (2025-2026)</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>ChatGPT share declining (57% → 39%); Claude surging (2% → 10%); Gemini stable at ~25%</t>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Image gen declining (bundled into horizontal); video/music/coding/agents growing fast</t>
+          <t>AI Assistant</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Horizontal market is redistributing; vertical market is expanding into new categories</t>
+          <t>~$20-100+</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>$20 Pro; $100+ Team/Enterprise</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>$19B ARR</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>18.9M MAU; 500+ &gt;$1M/yr</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>80% rev from enterprise; massive enterprise ARPU</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>User Engagement</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>ChatGPT: 2.2x more sessions/user than competitors; Claude power users: 139 min/day</t>
+          <t>ElevenLabs</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Character.AI: 2 hrs/day; CapCut: deep creative sessions; Cursor: all-day developer tool</t>
+          <t>Voice / Audio</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Vertical apps drive deeper engagement within specific use cases</t>
+          <t>~$5-99</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>$5 Starter to $199 Scale</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>$330M ARR</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Wide tier spread; specialized voice/audio moat</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Defensibility</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Context lock-in (history, preferences); app store ecosystems; connector/plugin networks</t>
+          <t>Runway</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Specialized workflows, creative communities, professional data integrations</t>
+          <t>Video Generation</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Horizontal: platform effects; Vertical: domain expertise and niche moats</t>
+          <t>~$12-76</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>$12 Standard to $76 Unlimited</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>$112.6M (2025)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>150K paying users</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Subscription + pay-per-use hybrid</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Bundling Threat</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>N/A — these ARE the bundles; expanding into super-apps (shopping, travel, health)</t>
+          <t>ChatGPT</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>High — image gen already squeezed by ChatGPT/Gemini; Midjourney fell from top 10 to #46</t>
+          <t>AI Assistant</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Music, voice, coding remain defensible; image gen being commoditized</t>
+          <t>~$4-6 (blended)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>$20 Plus; $200 Pro</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>$25B ARR</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>22M paid; 955M MAU</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Low blended ARPU due to massive free base; testing ads</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Geographic Split</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Western: ChatGPT/Claude/Gemini; China: Doubao/Qwen/DeepSeek; Russia: Yandex Alice</t>
+          <t>Suno</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CapCut (global via ByteDance); Canva (global); most coding tools US-centric</t>
+          <t>Music Generation</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Horizontal apps fragment by geography; vertical apps more globally distributed</t>
+          <t>~$12.50</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>$10 Pro; $30 Premier</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>$300M ARR</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>2M paid subs</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Defensible niche; high conversion from 100M+ total users</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Emerging Trend</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>AI browsers (Atlas, Comet, Dia); desktop agents; embedded AI in OS</t>
+          <t>Perplexity</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Agentic tools (OpenClaw, Manus, Genspark); vibe coding; AI notetakers</t>
+          <t>AI Search</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Both categories moving toward agentic, always-on AI beyond browser/app</t>
+          <t>~$15-20 (est.)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>$20 Pro; $200 Max</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>$450M ARR</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>30M+ MAU</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>60-65% rev from subscriptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Lovable</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>App Builder</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>~$25-50</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>$25 Pro; $50 Business</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>$400M ARR</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>~8M users</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Vibe coding; 100K+ projects/day</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Notion</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Productivity</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>~$10-18</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>$10 Plus; $18 Business; AI $10 add-on</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>$500-540M ARR</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>4M+ paying; 100M total</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>AI add-on drives incremental ARPU; 50% attach rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Grammarly</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Writing Assistant</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>~$1.46 (blended)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>$12 Premium; $15 Business</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>$700M+ rev</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>40M DAU</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Low blended due to massive free tier; profitable</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>GitHub Copilot</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Code Assistant</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>~$10-39</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>$10 Individual; $19 Business; $39 Enterprise</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>~$500M-1B (est.)</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>4.7M paid subs</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>90% Fortune 100; widest developer reach</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Midjourney</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Image Generation</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>~$10</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>$10-60/mo tiers</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>$500M rev (2025)</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>~12M active</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>$120/yr ARPU; 40 employees; no VC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Synthesia</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>AI Video (Enterprise)</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>~$22-100+</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>$22 Starter; enterprise custom</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>$100M+ ARR</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>70% Fortune 100; enterprise-heavy</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Otter.ai</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Meeting AI</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>~$8-25</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>$8.33 Pro to $25 Enterprise</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>$100M+ ARR</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>35M total users</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>&lt;200 employees; $500K rev/employee</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Replit</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Code / App Builder</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>~$25</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>$25/mo Core</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>$265M ARR</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>150K+ paying</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>1,556% YoY growth; $9B valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Character.AI</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>AI Companion</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>~$0.13 (blended)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>$9.99/mo c.ai+</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>$32-50M rev</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>20M MAU</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Very low conversion; ARPU ceiling; 2 hrs/day engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Replika</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>AI Companion</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>~$19.99 (paid only)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>$19.99/mo Pro</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>~$35M rev</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>10M+ downloads</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Superfan paradox: high engagement = high cost per user</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Google Gemini</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Horizontal</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>~$1-2 (blended)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>$20 Advanced; $30 Enterprise</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>$1.2B subs rev (2025)</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>750M MAU (incl. Search AI)</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Massive free base via Android; 8M+ enterprise seats</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>CapCut</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Video Editing</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>~$0.09 (blended)</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>$2.49-7.49/mo</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>$815M rev (2025)</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>736M MAU</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Ultra-low blended ARPU; 81% mobile video editing share</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Canva</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Vertical</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>~$1.27 (blended)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>$15 Pro; $10/seat Teams</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>$4B rev (2025)</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>31M paying; 265M MAU</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Low blended; high absolute revenue; $40B+ valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Horizontal</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>API-based</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>API pricing (very low cost)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>$1.1B rev (2025)</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>132.6M MAU</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>55% from API; 28-32% net margin; open-source</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Grok</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Horizontal</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>AI Assistant</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Bundled with X</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>$8-16/mo (X Premium)</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>~$500M (xAI standalone)</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>64M MAU</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Integrated into X/Twitter; can't isolate Grok ARPU</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Horizontal vs Vertical Gen AI Apps — Comparative Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Horizontal Apps</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Vertical Apps</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Key Insight</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ARPU Range</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Blended: $1-6/mo (massive free bases); Paid: $20-200/mo</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Blended: $0.09 (CapCut) to $214 (Harvey); Paid: $5-200+/mo</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Vertical enterprise apps (Harvey, Synthesia) have 10-100x higher ARPU than horizontal; consumer verticals (CapCut, Canva) have lowest ARPU</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Revenue Scale</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ChatGPT: $25B ARR; Claude: $19B; Gemini: $1.2B subs; Copilot: $1.5-2.5B</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Cursor: $2B; CapCut: $815M; Grammarly: $700M+; Canva: $4B; Midjourney: $500M; Suno: $300M</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Horizontal apps lead on absolute revenue; top vertical apps approaching $1B+ via specialization</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Market Concentration</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Top 2 (ChatGPT + Gemini) hold ~64% of US DAU share</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Fragmented; CapCut dominates video editing (81%) but each vertical has its own leaders</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Horizontal apps consolidate users; vertical apps compete within niches</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Total Downloads (2025)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>~1.35B+ (ChatGPT 845M + Gemini 305M + DeepSeek 110M + Grok 88M)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>CapCut alone: 509M; total across top 500 AI apps: 2.7B</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Horizontal chatbots dominate downloads but AI-enhanced tools have massive reach</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>MAU Scale</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>ChatGPT: 955M; Gemini: 750M; Doubao: 315M; Qwen: 203M; DeepSeek: 133M</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>CapCut: 736M; Canva: 265M; Picsart: 150M; Grammarly: 40M DAU</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>AI-enhanced creative tools rival horizontal assistants in scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Revenue Model</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Subscriptions ($20/mo); ChatGPT testing ads; transaction take-rate planned</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Subscription + credits (creative); enterprise contracts (legal/coding); freemium (productivity)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Vertical enterprise apps (Harvey $214/mo, Cursor $20-40) achieve far higher per-user monetization</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Growth Trajectory</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>ChatGPT share declining (57%→39%); Claude surging (2%→10%); Gemini stable ~25%</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Image gen declining (bundled); video/music/coding/legal AI growing fast</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Horizontal market redistributing; vertical market expanding into new categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>User Engagement</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>ChatGPT: 2.2x more sessions/user; Claude power users: 139 min/day</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Character.AI: 2 hrs/day; CapCut: deep sessions; Cursor: all-day dev tool</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Vertical apps drive deeper per-session engagement; companion apps face cost-scaling problem</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Defensibility</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Context lock-in; app store ecosystems; connector networks</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Specialized workflows; creative communities; professional data; domain expertise</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Horizontal: platform effects; Vertical: niche moats (music, voice, coding, legal most defensible)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Bundling Threat</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N/A — these ARE the bundles; expanding into super-apps</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>High for image gen (Midjourney #46 from top 10); low for music/voice/coding/legal</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ChatGPT/Gemini native image gen commoditizing standalone image apps; music, voice, legal remain safe</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Profitability</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>OpenAI: not profitable; Anthropic: 40% gross margins, break-even 2028; DeepSeek: 28-32% margin</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Midjourney: profitable (40 employees, no VC); Grammarly: profitable; Canva: profitable; Harvey: N/A</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Some verticals are already profitable with small teams; horizontals burning cash at scale</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2856,7 +5064,7 @@
           <t>ChatGPT</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>~57%</t>
         </is>
@@ -2898,7 +5106,7 @@
           <t>Google Gemini</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>~13%</t>
         </is>
@@ -2940,7 +5148,7 @@
           <t>Grok</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2982,7 +5190,7 @@
           <t>Microsoft Copilot</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3024,7 +5232,7 @@
           <t>Claude</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3066,7 +5274,7 @@
           <t>Perplexity</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3108,7 +5316,7 @@
           <t>DeepSeek</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3152,16 +5360,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
@@ -3196,7 +5404,7 @@
           <t>a16z</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Top 100 Gen AI Consumer Apps — 6th Edition (March 2026)</t>
         </is>
@@ -3213,7 +5421,7 @@
           <t>Apptopia</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Gen AI Chatbots Data Brief — March &amp; April 2026</t>
         </is>
@@ -3230,7 +5438,7 @@
           <t>AppTweak</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Most Downloaded AI Apps in 2025</t>
         </is>
@@ -3247,7 +5455,7 @@
           <t>AICPB</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>AI App Rankings by MAU — Issue 19 (Feb 2026)</t>
         </is>
@@ -3264,7 +5472,7 @@
           <t>SimilarWeb</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>AI Website Traffic Rankings (Jan 2026)</t>
         </is>
@@ -3281,7 +5489,7 @@
           <t>Yipit Data</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Referenced in a16z report</t>
         </is>
@@ -3298,7 +5506,7 @@
           <t>Sensor Tower</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Referenced in a16z report</t>
         </is>
@@ -3312,31 +5520,65 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Company Reports</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Various press releases and earnings</t>
+          <t>Sacra</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Company research profiles (2025-2026)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Revenue, WAU, and product announcements</t>
+          <t>Revenue, ARR, valuation, funding for private AI companies</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Company Reports / Press Releases</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Various (2025-2026)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Revenue, WAU, ARR, and product announcements</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Note: Some figures are estimates (marked with ~). Data may not be directly comparable across sources due to differing methodologies (web vs. mobile, DAU vs. MAU, global vs. US-only). Chinese app data primarily from AICPB. All data as of latest available (Jan–Mar 2026).</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Getlatka / CompWorth / Fueler</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Company financial profiles (2025-2026)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Revenue, employees, customers, funding data</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>ARPU Methodology: Blended ARPU = Total revenue / Total MAU (includes free users). Paid ARPU = Revenue / Paid subscribers only. Many apps have very low blended ARPU due to large free tiers but high paid-tier ARPU. Enterprise apps (Harvey, Cursor Business) have much higher effective ARPU due to seat-based pricing and custom contracts. Some figures are estimates (marked with ~). Data may not be directly comparable across sources due to differing methodologies. All data as of latest available (Jan–Apr 2026).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
